--- a/rules/CORE-000100/positive/01/data/unit-test-coreid-CG0423-positive.xlsx
+++ b/rules/CORE-000100/positive/01/data/unit-test-coreid-CG0423-positive.xlsx
@@ -96,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -113,6 +113,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -556,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,12 +614,12 @@
           <t>AGDOSU</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>AGTRTV</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>AGVAMT</t>
         </is>
@@ -622,63 +631,63 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Study Identifier</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Domain Abbreviation</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>Unique Subject Identifier</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>Sequence Number</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>Reported Agent Name</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>AG Pre-Specified</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>AG Occurrence</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>Dose per Administration</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>Dose Units</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>Treatment Vehicle</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K2" s="8" t="inlineStr">
         <is>
           <t>Treatment Vehicle
 Amount</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="L2" s="8" t="inlineStr">
         <is>
           <t>Treatment Vehicle
 Amount Units</t>
@@ -686,102 +695,102 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="5" t="n">
+      <c r="A4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="L4" s="4" t="n">
+      <c r="E4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="L4" s="8" t="n">
         <v>50</v>
       </c>
     </row>
@@ -827,12 +836,12 @@
           <t>tuberculin unit</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>SALINE</t>
         </is>
       </c>
-      <c r="K5" s="7" t="n">
+      <c r="K5" s="10" t="n">
         <v>0.1</v>
       </c>
       <c r="L5" t="inlineStr">
@@ -854,7 +863,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>XYZ-001-002</t>
+          <t>XYZ-001-003</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -879,62 +888,6 @@
         <v>5</v>
       </c>
       <c r="I6" t="inlineStr">
-        <is>
-          <t>tuberculin unit</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>SALINE</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>mL</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>AG</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>XYZ-001-003</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Tuberculin PPD-S</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" t="inlineStr">
         <is>
           <t>tuberculin unit</t>
         </is>
